--- a/2026/CABRERA/Septiembre/Septiembre CABRERA.xlsx
+++ b/2026/CABRERA/Septiembre/Septiembre CABRERA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\CABRERA\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\CABRERA\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1E5ECD-EFF1-41D3-A5DA-B16A5676542E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358C7D1A-5379-43F1-A5BC-DCB748964283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -22,11 +22,16 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$94</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="137">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -400,30 +405,9 @@
     <t>Aumentados en Jun10 a 108,000</t>
   </si>
   <si>
-    <t>Hace unos meses venimos arrastrando una diferencia de caja de $52.000 (Tenemos mas en el banco de lo que dice el excel)- Revisar</t>
-  </si>
-  <si>
-    <t>PREVISION ORDINARIA</t>
-  </si>
-  <si>
     <t>Mikel Jaureguiberry</t>
   </si>
   <si>
-    <t>Pinsur - Limpieza de tanque y cisterna</t>
-  </si>
-  <si>
-    <t>Transf 03/08</t>
-  </si>
-  <si>
-    <t>Debito 04/08</t>
-  </si>
-  <si>
-    <t>Transf 12/08</t>
-  </si>
-  <si>
-    <t>Transf 28/08</t>
-  </si>
-  <si>
     <t>VTO 16/10</t>
   </si>
   <si>
@@ -446,6 +430,21 @@
   </si>
   <si>
     <t>Transf 09/09</t>
+  </si>
+  <si>
+    <t>Transf 28/09</t>
+  </si>
+  <si>
+    <t>Transf 24/09</t>
+  </si>
+  <si>
+    <t>Transf 10/09</t>
+  </si>
+  <si>
+    <t>Debito 02/09</t>
+  </si>
+  <si>
+    <t>PREVISION ORDINARIA - AUMENTO SERVICIO DE LIMPIEZA</t>
   </si>
 </sst>
 </file>
@@ -459,7 +458,7 @@
     <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -605,13 +604,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -1040,7 +1032,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="175">
+  <cellXfs count="171">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1240,12 +1232,6 @@
     <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1283,6 +1269,45 @@
     <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1325,47 +1350,6 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="20" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="20" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1434,9 +1418,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1474,9 +1458,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1509,9 +1493,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1544,9 +1545,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1721,20 +1739,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L94"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="42.33203125" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="42.28515625" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="73" t="s">
         <v>50</v>
       </c>
@@ -1742,7 +1760,7 @@
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="70" t="s">
         <v>101</v>
       </c>
@@ -1750,7 +1768,7 @@
       <c r="C2" s="70"/>
       <c r="D2" s="70"/>
     </row>
-    <row r="3" spans="1:8" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="70" t="s">
         <v>56</v>
       </c>
@@ -1758,44 +1776,44 @@
       <c r="C3" s="70"/>
       <c r="D3" s="70"/>
     </row>
-    <row r="4" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="137" t="s">
+    <row r="4" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="135" t="s">
         <v>107</v>
       </c>
-      <c r="B4" s="137"/>
+      <c r="B4" s="135"/>
       <c r="C4" s="71"/>
       <c r="D4" s="71"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="137"/>
-      <c r="B5" s="137"/>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="135"/>
+      <c r="B5" s="135"/>
       <c r="C5" s="71"/>
       <c r="D5" s="71"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="137"/>
-      <c r="B6" s="137"/>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="135"/>
+      <c r="B6" s="135"/>
       <c r="C6" s="71"/>
       <c r="D6" s="71"/>
     </row>
-    <row r="7" spans="1:8" ht="6.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="137"/>
-      <c r="B7" s="137"/>
+    <row r="7" spans="1:8" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="135"/>
+      <c r="B7" s="135"/>
       <c r="C7" s="71"/>
       <c r="D7" s="71"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B9" s="145" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B10" s="145"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="145"/>
-    </row>
-    <row r="13" spans="1:8" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="143" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B10" s="143"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="143"/>
+    </row>
+    <row r="13" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F13" t="s">
         <v>98</v>
       </c>
@@ -1806,51 +1824,51 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="138" t="s">
+    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="136" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="138"/>
-      <c r="C14" s="138"/>
-      <c r="D14" s="138"/>
-    </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="138"/>
-      <c r="B15" s="138"/>
-      <c r="C15" s="138"/>
-      <c r="D15" s="138"/>
-    </row>
-    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="138"/>
-      <c r="B16" s="138"/>
-      <c r="C16" s="138"/>
-      <c r="D16" s="138"/>
-    </row>
-    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="138"/>
-      <c r="B17" s="138"/>
-      <c r="C17" s="138"/>
-      <c r="D17" s="138"/>
-    </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="136"/>
+      <c r="C14" s="136"/>
+      <c r="D14" s="136"/>
+    </row>
+    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="136"/>
+      <c r="B15" s="136"/>
+      <c r="C15" s="136"/>
+      <c r="D15" s="136"/>
+    </row>
+    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="136"/>
+      <c r="B16" s="136"/>
+      <c r="C16" s="136"/>
+      <c r="D16" s="136"/>
+    </row>
+    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="136"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="136"/>
+      <c r="D17" s="136"/>
+    </row>
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="60"/>
       <c r="B18" s="60"/>
       <c r="C18" s="60"/>
       <c r="D18" s="60"/>
     </row>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="133"/>
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="131"/>
       <c r="B19" s="60"/>
       <c r="C19" s="60"/>
       <c r="D19" s="60"/>
     </row>
-    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="60"/>
       <c r="B20" s="60"/>
       <c r="C20" s="60"/>
       <c r="D20" s="60"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="115" t="s">
         <v>15</v>
       </c>
@@ -1858,7 +1876,7 @@
       <c r="C21" s="64"/>
       <c r="D21" s="65"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>40</v>
       </c>
@@ -1866,43 +1884,44 @@
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
     </row>
-    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="45" t="s">
         <v>103</v>
       </c>
       <c r="B23" s="45"/>
-      <c r="C23" s="174">
+      <c r="C23" s="82">
         <v>475000</v>
       </c>
       <c r="D23" s="76" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="45"/>
       <c r="B24" s="45"/>
       <c r="C24" s="82"/>
       <c r="D24" s="72"/>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="45"/>
       <c r="B25" s="45"/>
       <c r="C25" s="82"/>
       <c r="D25" s="72"/>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="45"/>
       <c r="B26" s="45"/>
       <c r="C26" s="82"/>
       <c r="D26" s="72"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="45"/>
       <c r="B27" s="45"/>
       <c r="C27" s="83"/>
       <c r="D27" s="72"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="129" t="s">
         <v>41</v>
       </c>
@@ -1913,7 +1932,7 @@
       </c>
       <c r="D28" s="46"/>
     </row>
-    <row r="29" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
         <v>0</v>
       </c>
@@ -1926,7 +1945,7 @@
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>26</v>
       </c>
@@ -1935,23 +1954,23 @@
       <c r="D30" s="48"/>
       <c r="F30" s="4"/>
     </row>
-    <row r="31" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="107" t="s">
+        <v>125</v>
+      </c>
+      <c r="B31" s="108"/>
+      <c r="C31" s="132">
+        <v>108000</v>
+      </c>
+      <c r="D31" s="76" t="s">
         <v>132</v>
-      </c>
-      <c r="B31" s="108"/>
-      <c r="C31" s="134">
-        <v>108000</v>
-      </c>
-      <c r="D31" s="76" t="s">
-        <v>129</v>
       </c>
       <c r="F31" t="s">
         <v>122</v>
       </c>
       <c r="G31" s="4"/>
     </row>
-    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>22</v>
       </c>
@@ -1962,7 +1981,7 @@
         <v>108000</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>37</v>
       </c>
@@ -1970,19 +1989,19 @@
       <c r="C33" s="10"/>
       <c r="D33" s="29"/>
     </row>
-    <row r="34" spans="1:6" s="15" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="143" t="s">
+    <row r="34" spans="1:6" s="15" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="141" t="s">
         <v>116</v>
       </c>
-      <c r="B34" s="144"/>
-      <c r="C34" s="135">
+      <c r="B34" s="142"/>
+      <c r="C34" s="133">
         <v>87671</v>
       </c>
       <c r="D34" s="80" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>1</v>
       </c>
@@ -1993,7 +2012,7 @@
         <v>87671</v>
       </c>
     </row>
-    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
         <v>23</v>
       </c>
@@ -2001,48 +2020,48 @@
       <c r="C36" s="13"/>
       <c r="D36" s="50"/>
     </row>
-    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="45" t="s">
         <v>51</v>
       </c>
       <c r="B37" s="45" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C37" s="102"/>
       <c r="D37" s="80"/>
       <c r="F37" s="74"/>
     </row>
-    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="45" t="s">
         <v>52</v>
       </c>
       <c r="B38" s="45" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C38" s="84"/>
       <c r="D38" s="80"/>
     </row>
-    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="45" t="s">
         <v>53</v>
       </c>
       <c r="B39" s="45" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C39" s="84"/>
       <c r="D39" s="80"/>
     </row>
-    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="45" t="s">
         <v>54</v>
       </c>
       <c r="B40" s="45" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C40" s="84"/>
       <c r="D40" s="79"/>
     </row>
-    <row r="41" spans="1:6" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>2</v>
       </c>
@@ -2053,7 +2072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>25</v>
       </c>
@@ -2061,109 +2080,109 @@
       <c r="C42" s="13"/>
       <c r="D42" s="50"/>
     </row>
-    <row r="43" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="60" t="s">
         <v>95</v>
       </c>
       <c r="B43" s="45"/>
       <c r="C43" s="84">
-        <v>112437.87</v>
+        <v>120840</v>
       </c>
       <c r="D43" s="78" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="45" t="s">
         <v>94</v>
       </c>
       <c r="B44" s="45"/>
-      <c r="C44" s="173">
+      <c r="C44" s="84">
         <v>383461.24</v>
       </c>
       <c r="D44" s="78" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="B45" s="45"/>
+      <c r="C45" s="84">
+        <v>426982.58</v>
+      </c>
+      <c r="D45" s="78" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="B45" s="45"/>
-      <c r="C45" s="173">
-        <v>327154.65999999997</v>
-      </c>
-      <c r="D45" s="78" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="8" t="s">
+      <c r="B46" s="45"/>
+      <c r="C46" s="84">
+        <v>331424.7</v>
+      </c>
+      <c r="D46" s="78" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="8" t="s">
         <v>3</v>
-      </c>
-      <c r="B46" s="8"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="49">
-        <f>SUM(C43:C45)</f>
-        <v>823053.77</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="B47" s="8"/>
       <c r="C47" s="12"/>
-      <c r="D47" s="52"/>
-    </row>
-    <row r="48" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="143" t="s">
+      <c r="D47" s="49">
+        <f>SUM(C43:C46)</f>
+        <v>1262708.52</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B48" s="8"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="52"/>
+    </row>
+    <row r="49" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="B48" s="144"/>
-      <c r="C48" s="173">
+      <c r="B49" s="142"/>
+      <c r="C49" s="84">
         <v>73200</v>
       </c>
-      <c r="D48" s="78" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="64.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="143" t="s">
-        <v>136</v>
-      </c>
-      <c r="B49" s="144"/>
-      <c r="C49" s="173">
+      <c r="D49" s="78" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="141" t="s">
+        <v>129</v>
+      </c>
+      <c r="B50" s="142"/>
+      <c r="C50" s="84">
         <v>75000</v>
       </c>
-      <c r="D49" s="78" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="131" t="s">
-        <v>126</v>
-      </c>
-      <c r="B50" s="132"/>
-      <c r="C50" s="84">
-        <v>540000</v>
-      </c>
       <c r="D50" s="78" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
         <v>8</v>
       </c>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
       <c r="D51" s="55">
-        <f>SUM(C48:C50)</f>
-        <v>688200</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f>SUM(C49:C50)</f>
+        <v>148200</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
         <v>18</v>
       </c>
@@ -2171,7 +2190,7 @@
       <c r="C52" s="6"/>
       <c r="D52" s="52"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="45" t="s">
         <v>97</v>
       </c>
@@ -2181,17 +2200,18 @@
       </c>
       <c r="D53" s="56"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="45" t="s">
         <v>96</v>
       </c>
       <c r="B54" s="45"/>
       <c r="C54" s="84">
-        <v>46280.02</v>
+        <f>48778.75-8362</f>
+        <v>40416.75</v>
       </c>
       <c r="D54" s="54"/>
     </row>
-    <row r="55" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="111" t="s">
         <v>22</v>
       </c>
@@ -2199,34 +2219,33 @@
       <c r="C55" s="57"/>
       <c r="D55" s="49">
         <f>SUM(C53:C54)</f>
-        <v>115280.01999999999</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>109416.75</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="45"/>
       <c r="B56" s="45"/>
       <c r="C56" s="45"/>
       <c r="D56" s="58"/>
     </row>
-    <row r="57" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="139" t="s">
-        <v>124</v>
-      </c>
-      <c r="B57" s="140"/>
-      <c r="C57" s="141"/>
+    <row r="57" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="137" t="s">
+        <v>136</v>
+      </c>
+      <c r="B57" s="138"/>
+      <c r="C57" s="139"/>
       <c r="D57" s="59">
-        <f>2300000-1903013.6</f>
-        <v>396986.39999999991</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>76000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="112"/>
       <c r="B58" s="60"/>
       <c r="C58" s="60"/>
       <c r="D58" s="61"/>
       <c r="E58" s="18"/>
     </row>
-    <row r="59" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="113" t="s">
         <v>19</v>
       </c>
@@ -2234,25 +2253,25 @@
       <c r="C59" s="62"/>
       <c r="D59" s="63">
         <f>(SUM(D24:D57))</f>
-        <v>2694191.19</v>
+        <v>2266996.27</v>
       </c>
       <c r="E59" s="18"/>
       <c r="F59" s="18"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="60"/>
       <c r="B60" s="60"/>
       <c r="C60" s="60"/>
       <c r="D60" s="60"/>
       <c r="F60" s="75"/>
     </row>
-    <row r="61" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="60"/>
       <c r="B61" s="60"/>
       <c r="C61" s="60"/>
       <c r="D61" s="60"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="115" t="s">
         <v>27</v>
       </c>
@@ -2260,25 +2279,25 @@
       <c r="C62" s="64"/>
       <c r="D62" s="65"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="143"/>
-      <c r="B63" s="144"/>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="141"/>
+      <c r="B63" s="142"/>
       <c r="C63" s="53"/>
       <c r="D63" s="51"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="143"/>
-      <c r="B64" s="144"/>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="141"/>
+      <c r="B64" s="142"/>
       <c r="C64" s="53"/>
       <c r="D64" s="51"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="117"/>
       <c r="B65" s="118"/>
       <c r="C65" s="53"/>
       <c r="D65" s="51"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="119"/>
       <c r="B66" s="120"/>
       <c r="C66" s="121"/>
@@ -2287,17 +2306,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="60"/>
       <c r="B67" s="60"/>
       <c r="C67" s="60"/>
     </row>
-    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="60"/>
       <c r="B68" s="60"/>
       <c r="C68" s="60"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="122" t="s">
         <v>28</v>
       </c>
@@ -2305,12 +2324,12 @@
       <c r="C69" s="123"/>
       <c r="D69" s="81"/>
     </row>
-    <row r="70" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="60"/>
       <c r="B70" s="60"/>
       <c r="C70" s="60"/>
     </row>
-    <row r="71" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="113" t="s">
         <v>29</v>
       </c>
@@ -2321,32 +2340,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="60"/>
       <c r="B72" s="60"/>
       <c r="C72" s="60"/>
     </row>
-    <row r="73" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="124" t="s">
         <v>20</v>
       </c>
       <c r="B73" s="125">
         <f>D59</f>
-        <v>2694191.19</v>
+        <v>2266996.27</v>
       </c>
       <c r="C73" s="126"/>
     </row>
-    <row r="74" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="124" t="s">
         <v>21</v>
       </c>
       <c r="B74" s="125">
         <f>D59-D57</f>
-        <v>2297204.79</v>
+        <v>2190996.27</v>
       </c>
       <c r="C74" s="60"/>
     </row>
-    <row r="75" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="124" t="s">
         <v>30</v>
       </c>
@@ -2356,7 +2375,7 @@
       </c>
       <c r="C75" s="60"/>
     </row>
-    <row r="76" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="124" t="s">
         <v>45</v>
       </c>
@@ -2366,52 +2385,50 @@
       </c>
       <c r="C76" s="60"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="60"/>
       <c r="B77" s="60"/>
       <c r="C77" s="60"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="60"/>
       <c r="B78" s="60"/>
       <c r="C78" s="60"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="60"/>
       <c r="B79" s="60"/>
       <c r="C79" s="60"/>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="127" t="s">
         <v>39</v>
       </c>
       <c r="B80" s="128"/>
       <c r="C80" s="60"/>
     </row>
-    <row r="81" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="96" t="s">
         <v>121</v>
       </c>
       <c r="B81" s="68">
-        <v>587909.48</v>
+        <v>112864.41000000015</v>
       </c>
       <c r="C81" s="126"/>
       <c r="D81" s="18"/>
-      <c r="G81" s="136" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G81" s="134"/>
+    </row>
+    <row r="82" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="97" t="s">
         <v>48</v>
       </c>
       <c r="B82" s="16">
         <f>PRORRATEO!G18</f>
-        <v>1427968.5300000003</v>
-      </c>
-      <c r="G82" s="136"/>
-    </row>
-    <row r="83" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2141344.5600000005</v>
+      </c>
+      <c r="G82" s="134"/>
+    </row>
+    <row r="83" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="97" t="s">
         <v>47</v>
       </c>
@@ -2419,19 +2436,19 @@
         <f>B93</f>
         <v>0</v>
       </c>
-      <c r="G83" s="136"/>
-    </row>
-    <row r="84" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G83" s="134"/>
+    </row>
+    <row r="84" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
         <v>31</v>
       </c>
       <c r="B84" s="77">
         <f>-B74</f>
-        <v>-2297204.79</v>
-      </c>
-      <c r="G84" s="136"/>
-    </row>
-    <row r="85" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>-2190996.27</v>
+      </c>
+      <c r="G84" s="134"/>
+    </row>
+    <row r="85" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
         <v>32</v>
       </c>
@@ -2439,43 +2456,43 @@
         <f>-(B75)</f>
         <v>0</v>
       </c>
-      <c r="G85" s="136"/>
-    </row>
-    <row r="86" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G85" s="134"/>
+    </row>
+    <row r="86" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="98" t="s">
         <v>8</v>
       </c>
       <c r="B86" s="68">
         <f>SUM(B81:B85)</f>
-        <v>-281326.7799999998</v>
+        <v>63212.700000000652</v>
       </c>
       <c r="C86" s="18"/>
       <c r="D86" s="18"/>
-      <c r="G86" s="136"/>
-    </row>
-    <row r="87" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G86" s="134"/>
+    </row>
+    <row r="87" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="17"/>
       <c r="C87" s="18"/>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A89" s="142" t="s">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A89" s="140" t="s">
         <v>38</v>
       </c>
-      <c r="B89" s="142"/>
-    </row>
-    <row r="90" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="142"/>
-      <c r="B90" s="142"/>
-    </row>
-    <row r="91" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B89" s="140"/>
+    </row>
+    <row r="90" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="140"/>
+      <c r="B90" s="140"/>
+    </row>
+    <row r="91" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="66"/>
       <c r="B91" s="11"/>
     </row>
-    <row r="92" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="66"/>
       <c r="B92" s="11"/>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" s="19" t="s">
         <v>8</v>
       </c>
@@ -2484,7 +2501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L94" s="3"/>
     </row>
   </sheetData>
@@ -2498,8 +2515,8 @@
     <mergeCell ref="A63:B63"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A48:B48"/>
     <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2510,72 +2527,72 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" customWidth="1"/>
-    <col min="4" max="4" width="18.5546875" customWidth="1"/>
-    <col min="5" max="5" width="5.109375" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.28515625" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="5" max="5" width="5.140625" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="14.109375" customWidth="1"/>
-    <col min="10" max="10" width="14.33203125" customWidth="1"/>
-    <col min="11" max="11" width="14.109375" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" customWidth="1"/>
-    <col min="13" max="13" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.33203125" customWidth="1"/>
-    <col min="15" max="15" width="14.109375" customWidth="1"/>
-    <col min="16" max="16" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" customWidth="1"/>
+    <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.28515625" customWidth="1"/>
+    <col min="15" max="15" width="14.140625" customWidth="1"/>
+    <col min="16" max="16" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
-      <c r="B1" s="150" t="str">
+      <c r="B1" s="161" t="str">
         <f>RESUMEN!A4</f>
         <v>Banco: Santander
 C.U.I.T.   30-71774143-5
 CBU: 0720533020000000956840 ALIAS: BLONDA.LAGO.CORO
 Nº de cuenta: 533-009568/4</v>
       </c>
-      <c r="C1" s="151"/>
-      <c r="D1" s="151"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="150" t="s">
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
+      <c r="F1" s="161" t="s">
         <v>111</v>
       </c>
-      <c r="G1" s="151"/>
-      <c r="H1" s="151"/>
-      <c r="I1" s="152"/>
-      <c r="J1" s="146" t="s">
+      <c r="G1" s="162"/>
+      <c r="H1" s="162"/>
+      <c r="I1" s="163"/>
+      <c r="J1" s="157" t="s">
         <v>108</v>
       </c>
-      <c r="K1" s="147"/>
+      <c r="K1" s="158"/>
       <c r="L1" s="103" t="s">
         <v>109</v>
       </c>
       <c r="M1" s="103"/>
       <c r="N1" s="105">
-        <v>2300000</v>
+        <v>2266996.27</v>
       </c>
       <c r="O1" s="99"/>
       <c r="P1" s="4"/>
     </row>
-    <row r="2" spans="1:18" ht="43.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="43.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
-      <c r="D2" s="154"/>
-      <c r="E2" s="155"/>
-      <c r="F2" s="153"/>
-      <c r="G2" s="154"/>
-      <c r="H2" s="154"/>
-      <c r="I2" s="155"/>
-      <c r="J2" s="148"/>
-      <c r="K2" s="149"/>
+      <c r="B2" s="164"/>
+      <c r="C2" s="165"/>
+      <c r="D2" s="165"/>
+      <c r="E2" s="166"/>
+      <c r="F2" s="164"/>
+      <c r="G2" s="165"/>
+      <c r="H2" s="165"/>
+      <c r="I2" s="166"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="160"/>
       <c r="L2" s="104" t="s">
         <v>110</v>
       </c>
@@ -2583,75 +2600,75 @@
       <c r="N2" s="85"/>
       <c r="O2" s="100"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="156" t="s">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="167" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="158" t="s">
+      <c r="B3" s="169" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="160" t="s">
+      <c r="C3" s="147" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="160" t="s">
+      <c r="D3" s="147" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="160" t="s">
+      <c r="E3" s="147" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="160" t="s">
+      <c r="F3" s="147" t="s">
         <v>46</v>
       </c>
-      <c r="G3" s="160" t="s">
+      <c r="G3" s="147" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="160" t="s">
+      <c r="H3" s="147" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="168" t="s">
+      <c r="I3" s="152" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="166" t="s">
+      <c r="J3" s="149" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="166" t="s">
+      <c r="K3" s="149" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="166" t="s">
+      <c r="L3" s="149" t="s">
         <v>33</v>
       </c>
-      <c r="M3" s="171" t="s">
+      <c r="M3" s="155" t="s">
         <v>44</v>
       </c>
       <c r="N3" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="O3" s="162" t="s">
+      <c r="O3" s="144" t="s">
         <v>42</v>
       </c>
       <c r="R3" s="18"/>
     </row>
-    <row r="4" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="157"/>
-      <c r="B4" s="159"/>
-      <c r="C4" s="161"/>
-      <c r="D4" s="161"/>
-      <c r="E4" s="165"/>
-      <c r="F4" s="161"/>
-      <c r="G4" s="161"/>
-      <c r="H4" s="165"/>
-      <c r="I4" s="169"/>
-      <c r="J4" s="167"/>
-      <c r="K4" s="170"/>
-      <c r="L4" s="167"/>
-      <c r="M4" s="172"/>
+    <row r="4" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="168"/>
+      <c r="B4" s="170"/>
+      <c r="C4" s="151"/>
+      <c r="D4" s="151"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="151"/>
+      <c r="G4" s="151"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="153"/>
+      <c r="J4" s="150"/>
+      <c r="K4" s="154"/>
+      <c r="L4" s="150"/>
+      <c r="M4" s="156"/>
       <c r="N4" s="24" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 16/10</v>
       </c>
-      <c r="O4" s="163"/>
-    </row>
-    <row r="5" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O4" s="145"/>
+    </row>
+    <row r="5" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -2668,19 +2685,19 @@
         <v>6.84</v>
       </c>
       <c r="F5" s="32">
-        <v>246710.01</v>
+        <v>411308.01</v>
       </c>
       <c r="G5" s="33">
-        <v>0</v>
+        <v>110000</v>
       </c>
       <c r="H5" s="34"/>
       <c r="I5" s="35">
         <f>F5-G5</f>
-        <v>246710.01</v>
+        <v>301308.01</v>
       </c>
       <c r="J5" s="35">
         <f>IF(I5&gt;0,I5*2.95%,0)</f>
-        <v>7277.9452950000004</v>
+        <v>8888.586295000001</v>
       </c>
       <c r="K5" s="36">
         <f t="shared" ref="K5:K16" si="0">N$2*E5%</f>
@@ -2688,18 +2705,18 @@
       </c>
       <c r="L5" s="36">
         <f t="shared" ref="L5:L16" si="1">N$1*E5%</f>
-        <v>157320</v>
+        <v>155062.544868</v>
       </c>
       <c r="M5" s="37">
         <v>0</v>
       </c>
       <c r="N5" s="38">
         <f>ROUND(I5+J5+K5+L5+M5,0) + P5</f>
-        <v>411308.01</v>
+        <v>465259.01</v>
       </c>
       <c r="O5" s="39">
         <f t="shared" ref="O5:O16" si="2">ROUND(N5*3%,0) + N5</f>
-        <v>423647.01</v>
+        <v>479217.01</v>
       </c>
       <c r="P5" s="18">
         <v>0.01</v>
@@ -2708,7 +2725,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -2725,11 +2742,11 @@
         <v>7.79</v>
       </c>
       <c r="F6" s="32">
-        <v>152449.01999999999</v>
+        <v>184545.02</v>
       </c>
       <c r="G6" s="33">
         <f>F6</f>
-        <v>152449.01999999999</v>
+        <v>184545.02</v>
       </c>
       <c r="H6" s="34"/>
       <c r="I6" s="87">
@@ -2746,18 +2763,18 @@
       </c>
       <c r="L6" s="88">
         <f t="shared" si="1"/>
-        <v>179170</v>
+        <v>176599.009433</v>
       </c>
       <c r="M6" s="89">
         <v>0</v>
       </c>
       <c r="N6" s="90">
         <f t="shared" ref="N6:N16" si="5">ROUND(SUM(I6:M6),0) + P6</f>
-        <v>179170.02</v>
+        <v>176599.02</v>
       </c>
       <c r="O6" s="91">
         <f t="shared" si="2"/>
-        <v>184545.02</v>
+        <v>181897.02</v>
       </c>
       <c r="P6" s="18">
         <f>P5+0.01</f>
@@ -2767,7 +2784,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="106" t="s">
         <v>10</v>
       </c>
@@ -2784,15 +2801,16 @@
         <v>6.75</v>
       </c>
       <c r="F7" s="33">
-        <v>110570.03</v>
+        <v>155249.03</v>
       </c>
       <c r="G7" s="33">
-        <v>110571</v>
+        <f>F7</f>
+        <v>155249.03</v>
       </c>
       <c r="H7" s="34"/>
       <c r="I7" s="35">
         <f t="shared" si="3"/>
-        <v>-0.97000000000116415</v>
+        <v>0</v>
       </c>
       <c r="J7" s="35">
         <f t="shared" si="4"/>
@@ -2804,18 +2822,18 @@
       </c>
       <c r="L7" s="36">
         <f t="shared" si="1"/>
-        <v>155250</v>
+        <v>153022.24822500002</v>
       </c>
       <c r="M7" s="37">
         <v>0</v>
       </c>
       <c r="N7" s="38">
         <f t="shared" si="5"/>
-        <v>155249.03</v>
+        <v>153022.03</v>
       </c>
       <c r="O7" s="39">
         <f t="shared" si="2"/>
-        <v>159906.03</v>
+        <v>157613.03</v>
       </c>
       <c r="P7" s="18">
         <f t="shared" ref="P7:P16" si="6">P6+0.01</f>
@@ -2826,7 +2844,7 @@
       </c>
       <c r="R7" s="18"/>
     </row>
-    <row r="8" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
@@ -2843,20 +2861,20 @@
         <v>7.41</v>
       </c>
       <c r="F8" s="33">
-        <v>140790.04</v>
+        <v>170430.04</v>
       </c>
       <c r="G8" s="33">
-        <f>F8</f>
-        <v>140790.04</v>
+        <f>F8-400</f>
+        <v>170030.04</v>
       </c>
       <c r="H8" s="34"/>
       <c r="I8" s="35">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="J8" s="35">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="K8" s="36">
         <f t="shared" si="0"/>
@@ -2864,18 +2882,18 @@
       </c>
       <c r="L8" s="36">
         <f t="shared" si="1"/>
-        <v>170430</v>
+        <v>167984.423607</v>
       </c>
       <c r="M8" s="37">
         <v>0</v>
       </c>
       <c r="N8" s="38">
         <f t="shared" si="5"/>
-        <v>170430.04</v>
+        <v>168396.04</v>
       </c>
       <c r="O8" s="39">
         <f t="shared" si="2"/>
-        <v>175543.04000000001</v>
+        <v>173448.04</v>
       </c>
       <c r="P8" s="18">
         <f t="shared" si="6"/>
@@ -2886,7 +2904,7 @@
       </c>
       <c r="R8" s="18"/>
     </row>
-    <row r="9" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="106" t="s">
         <v>11</v>
       </c>
@@ -2903,19 +2921,20 @@
         <v>8</v>
       </c>
       <c r="F9" s="32">
-        <v>196000.05</v>
+        <v>228000.05</v>
       </c>
       <c r="G9" s="33">
-        <v>197000</v>
+        <f>43000+185000</f>
+        <v>228000</v>
       </c>
       <c r="H9" s="34"/>
       <c r="I9" s="35">
         <f t="shared" si="3"/>
-        <v>-999.95000000001164</v>
+        <v>4.9999999988358468E-2</v>
       </c>
       <c r="J9" s="35">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.4749999996565748E-3</v>
       </c>
       <c r="K9" s="36">
         <f t="shared" si="0"/>
@@ -2923,18 +2942,18 @@
       </c>
       <c r="L9" s="36">
         <f t="shared" si="1"/>
-        <v>184000</v>
+        <v>181359.7016</v>
       </c>
       <c r="M9" s="37">
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="N9" s="38">
         <f t="shared" si="5"/>
-        <v>228000.05</v>
+        <v>181360.05</v>
       </c>
       <c r="O9" s="39">
         <f t="shared" si="2"/>
-        <v>234840.05</v>
+        <v>186801.05</v>
       </c>
       <c r="P9" s="18">
         <f t="shared" si="6"/>
@@ -2944,7 +2963,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -2961,20 +2980,17 @@
         <v>6.97</v>
       </c>
       <c r="F10" s="32">
-        <v>155051.06</v>
-      </c>
-      <c r="G10" s="33">
-        <f>72000+60000</f>
-        <v>132000</v>
-      </c>
+        <v>184041.06</v>
+      </c>
+      <c r="G10" s="33"/>
       <c r="H10" s="34"/>
       <c r="I10" s="35">
         <f t="shared" si="3"/>
-        <v>23051.059999999998</v>
+        <v>184041.06</v>
       </c>
       <c r="J10" s="35">
         <f t="shared" si="4"/>
-        <v>680.00626999999997</v>
+        <v>5429.2112700000007</v>
       </c>
       <c r="K10" s="36">
         <f t="shared" si="0"/>
@@ -2982,18 +2998,18 @@
       </c>
       <c r="L10" s="36">
         <f t="shared" si="1"/>
-        <v>160310</v>
+        <v>158009.64001899998</v>
       </c>
       <c r="M10" s="37">
         <v>0</v>
       </c>
       <c r="N10" s="38">
         <f t="shared" si="5"/>
-        <v>184041.06</v>
+        <v>347480.06</v>
       </c>
       <c r="O10" s="39">
         <f t="shared" si="2"/>
-        <v>189562.06</v>
+        <v>357904.06</v>
       </c>
       <c r="P10" s="18">
         <f t="shared" si="6"/>
@@ -3002,7 +3018,7 @@
       <c r="Q10" s="75"/>
       <c r="R10" s="74"/>
     </row>
-    <row r="11" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -3019,11 +3035,11 @@
         <v>6.75</v>
       </c>
       <c r="F11" s="32">
-        <v>128250.07</v>
+        <v>155250.07</v>
       </c>
       <c r="G11" s="33">
         <f>F11</f>
-        <v>128250.07</v>
+        <v>155250.07</v>
       </c>
       <c r="H11" s="34"/>
       <c r="I11" s="35">
@@ -3040,18 +3056,18 @@
       </c>
       <c r="L11" s="36">
         <f t="shared" si="1"/>
-        <v>155250</v>
+        <v>153022.24822500002</v>
       </c>
       <c r="M11" s="37">
         <v>0</v>
       </c>
       <c r="N11" s="38">
         <f t="shared" si="5"/>
-        <v>155250.07</v>
+        <v>153022.07</v>
       </c>
       <c r="O11" s="39">
         <f t="shared" si="2"/>
-        <v>159908.07</v>
+        <v>157613.07</v>
       </c>
       <c r="P11" s="18">
         <f t="shared" si="6"/>
@@ -3061,7 +3077,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
@@ -3078,11 +3094,11 @@
         <v>7.79</v>
       </c>
       <c r="F12" s="32">
-        <v>148010.07999999999</v>
+        <v>179170.08</v>
       </c>
       <c r="G12" s="33">
         <f>F12</f>
-        <v>148010.07999999999</v>
+        <v>179170.08</v>
       </c>
       <c r="H12" s="34"/>
       <c r="I12" s="35">
@@ -3099,25 +3115,25 @@
       </c>
       <c r="L12" s="36">
         <f t="shared" si="1"/>
-        <v>179170</v>
+        <v>176599.009433</v>
       </c>
       <c r="M12" s="37">
         <v>0</v>
       </c>
       <c r="N12" s="38">
         <f t="shared" si="5"/>
-        <v>179170.08</v>
+        <v>176599.08</v>
       </c>
       <c r="O12" s="39">
         <f t="shared" si="2"/>
-        <v>184545.08</v>
+        <v>181897.08</v>
       </c>
       <c r="P12" s="18">
         <f t="shared" si="6"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
@@ -3134,11 +3150,11 @@
         <v>7.62</v>
       </c>
       <c r="F13" s="33">
-        <v>149123.09</v>
+        <v>175260.09</v>
       </c>
       <c r="G13" s="33">
         <f>F13</f>
-        <v>149123.09</v>
+        <v>175260.09</v>
       </c>
       <c r="H13" s="34"/>
       <c r="I13" s="35">
@@ -3155,18 +3171,18 @@
       </c>
       <c r="L13" s="36">
         <f t="shared" si="1"/>
-        <v>175260</v>
+        <v>172745.11577400001</v>
       </c>
       <c r="M13" s="37">
         <v>0</v>
       </c>
       <c r="N13" s="38">
         <f t="shared" si="5"/>
-        <v>175260.09</v>
+        <v>172745.09</v>
       </c>
       <c r="O13" s="39">
         <f t="shared" si="2"/>
-        <v>180518.09</v>
+        <v>177927.09</v>
       </c>
       <c r="P13" s="18">
         <f t="shared" si="6"/>
@@ -3176,7 +3192,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -3193,19 +3209,19 @@
         <v>6.97</v>
       </c>
       <c r="F14" s="32">
-        <v>132430.1</v>
+        <v>296647.09999999998</v>
       </c>
       <c r="G14" s="33">
-        <v>0</v>
+        <v>160310</v>
       </c>
       <c r="H14" s="34"/>
       <c r="I14" s="35">
         <f t="shared" si="3"/>
-        <v>132430.1</v>
+        <v>136337.09999999998</v>
       </c>
       <c r="J14" s="35">
         <f t="shared" si="4"/>
-        <v>3906.6879500000005</v>
+        <v>4021.9444499999995</v>
       </c>
       <c r="K14" s="36">
         <f t="shared" si="0"/>
@@ -3213,28 +3229,28 @@
       </c>
       <c r="L14" s="36">
         <f t="shared" si="1"/>
-        <v>160310</v>
+        <v>158009.64001899998</v>
       </c>
       <c r="M14" s="37">
         <v>0</v>
       </c>
       <c r="N14" s="38">
         <f t="shared" si="5"/>
-        <v>296647.09999999998</v>
+        <v>298369.09999999998</v>
       </c>
       <c r="O14" s="39">
         <f t="shared" si="2"/>
-        <v>305546.09999999998</v>
+        <v>307320.09999999998</v>
       </c>
       <c r="P14" s="18">
         <f t="shared" si="6"/>
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="Q14" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -3251,11 +3267,11 @@
         <v>14.01</v>
       </c>
       <c r="F15" s="32">
-        <v>20875.11</v>
+        <v>322230.11</v>
       </c>
       <c r="G15" s="33">
         <f>F15</f>
-        <v>20875.11</v>
+        <v>322230.11</v>
       </c>
       <c r="H15" s="34"/>
       <c r="I15" s="35">
@@ -3272,18 +3288,18 @@
       </c>
       <c r="L15" s="36">
         <f t="shared" si="1"/>
-        <v>322230</v>
+        <v>317606.17742700002</v>
       </c>
       <c r="M15" s="37">
         <v>0</v>
       </c>
       <c r="N15" s="38">
         <f t="shared" si="5"/>
-        <v>322230.11</v>
+        <v>317606.11</v>
       </c>
       <c r="O15" s="39">
         <f t="shared" si="2"/>
-        <v>331897.11</v>
+        <v>327134.11</v>
       </c>
       <c r="P15" s="18">
         <f t="shared" si="6"/>
@@ -3293,7 +3309,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
@@ -3310,11 +3326,11 @@
         <v>13.1</v>
       </c>
       <c r="F16" s="32">
-        <v>248900.12</v>
+        <v>301300.12</v>
       </c>
       <c r="G16" s="33">
         <f>F16</f>
-        <v>248900.12</v>
+        <v>301300.12</v>
       </c>
       <c r="H16" s="34"/>
       <c r="I16" s="35">
@@ -3331,18 +3347,18 @@
       </c>
       <c r="L16" s="36">
         <f t="shared" si="1"/>
-        <v>301300</v>
+        <v>296976.51137000002</v>
       </c>
       <c r="M16" s="37">
         <v>0</v>
       </c>
       <c r="N16" s="38">
         <f t="shared" si="5"/>
-        <v>301300.12</v>
+        <v>296977.12</v>
       </c>
       <c r="O16" s="39">
         <f t="shared" si="2"/>
-        <v>310339.12</v>
+        <v>305886.12</v>
       </c>
       <c r="P16" s="18">
         <f t="shared" si="6"/>
@@ -3352,7 +3368,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -3372,7 +3388,7 @@
       <c r="O17" s="39"/>
       <c r="P17" s="18"/>
     </row>
-    <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="40"/>
       <c r="C18" s="41"/>
       <c r="D18" s="42"/>
@@ -3382,11 +3398,11 @@
       </c>
       <c r="F18" s="21">
         <f>SUM(F5:F17)</f>
-        <v>1829158.7800000007</v>
+        <v>2763430.7800000003</v>
       </c>
       <c r="G18" s="25">
         <f>SUM(G5:G17)</f>
-        <v>1427968.5300000003</v>
+        <v>2141344.5600000005</v>
       </c>
       <c r="H18" s="25">
         <f>SUM(H5:H17)</f>
@@ -3400,106 +3416,113 @@
       </c>
       <c r="L18" s="25">
         <f>SUM(L5:L17)</f>
-        <v>2300000</v>
+        <v>2266996.27</v>
       </c>
       <c r="M18" s="25">
         <f>SUM(M5:M17)</f>
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="N18" s="44">
         <f>SUM(N5:N17)</f>
-        <v>2758055.7800000003</v>
+        <v>2907434.7800000003</v>
       </c>
       <c r="O18" s="44">
         <f>SUM(O5:O17)</f>
-        <v>2840796.7800000003</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+        <v>2994657.7800000003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="D19" s="20"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D20" s="164" t="s">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D20" s="146" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="164"/>
-      <c r="F20" s="164"/>
-      <c r="G20" s="164"/>
-      <c r="H20" s="164"/>
-      <c r="I20" s="164"/>
-      <c r="J20" s="164"/>
-      <c r="K20" s="164"/>
-      <c r="L20" s="164"/>
-      <c r="M20" s="164"/>
-      <c r="N20" s="164"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D21" s="164"/>
-      <c r="E21" s="164"/>
-      <c r="F21" s="164"/>
-      <c r="G21" s="164"/>
-      <c r="H21" s="164"/>
-      <c r="I21" s="164"/>
-      <c r="J21" s="164"/>
-      <c r="K21" s="164"/>
-      <c r="L21" s="164"/>
-      <c r="M21" s="164"/>
-      <c r="N21" s="164"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D22" s="164"/>
-      <c r="E22" s="164"/>
-      <c r="F22" s="164"/>
-      <c r="G22" s="164"/>
-      <c r="H22" s="164"/>
-      <c r="I22" s="164"/>
-      <c r="J22" s="164"/>
-      <c r="K22" s="164"/>
-      <c r="L22" s="164"/>
-      <c r="M22" s="164"/>
-      <c r="N22" s="164"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D23" s="164"/>
-      <c r="E23" s="164"/>
-      <c r="F23" s="164"/>
-      <c r="G23" s="164"/>
-      <c r="H23" s="164"/>
-      <c r="I23" s="164"/>
-      <c r="J23" s="164"/>
-      <c r="K23" s="164"/>
-      <c r="L23" s="164"/>
-      <c r="M23" s="164"/>
-      <c r="N23" s="164"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D24" s="164"/>
-      <c r="E24" s="164"/>
-      <c r="F24" s="164"/>
-      <c r="G24" s="164"/>
-      <c r="H24" s="164"/>
-      <c r="I24" s="164"/>
-      <c r="J24" s="164"/>
-      <c r="K24" s="164"/>
-      <c r="L24" s="164"/>
-      <c r="M24" s="164"/>
-      <c r="N24" s="164"/>
-    </row>
-    <row r="25" spans="1:16" ht="4.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D25" s="164"/>
-      <c r="E25" s="164"/>
-      <c r="F25" s="164"/>
-      <c r="G25" s="164"/>
-      <c r="H25" s="164"/>
-      <c r="I25" s="164"/>
-      <c r="J25" s="164"/>
-      <c r="K25" s="164"/>
-      <c r="L25" s="164"/>
-      <c r="M25" s="164"/>
-      <c r="N25" s="164"/>
+      <c r="E20" s="146"/>
+      <c r="F20" s="146"/>
+      <c r="G20" s="146"/>
+      <c r="H20" s="146"/>
+      <c r="I20" s="146"/>
+      <c r="J20" s="146"/>
+      <c r="K20" s="146"/>
+      <c r="L20" s="146"/>
+      <c r="M20" s="146"/>
+      <c r="N20" s="146"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D21" s="146"/>
+      <c r="E21" s="146"/>
+      <c r="F21" s="146"/>
+      <c r="G21" s="146"/>
+      <c r="H21" s="146"/>
+      <c r="I21" s="146"/>
+      <c r="J21" s="146"/>
+      <c r="K21" s="146"/>
+      <c r="L21" s="146"/>
+      <c r="M21" s="146"/>
+      <c r="N21" s="146"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D22" s="146"/>
+      <c r="E22" s="146"/>
+      <c r="F22" s="146"/>
+      <c r="G22" s="146"/>
+      <c r="H22" s="146"/>
+      <c r="I22" s="146"/>
+      <c r="J22" s="146"/>
+      <c r="K22" s="146"/>
+      <c r="L22" s="146"/>
+      <c r="M22" s="146"/>
+      <c r="N22" s="146"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D23" s="146"/>
+      <c r="E23" s="146"/>
+      <c r="F23" s="146"/>
+      <c r="G23" s="146"/>
+      <c r="H23" s="146"/>
+      <c r="I23" s="146"/>
+      <c r="J23" s="146"/>
+      <c r="K23" s="146"/>
+      <c r="L23" s="146"/>
+      <c r="M23" s="146"/>
+      <c r="N23" s="146"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D24" s="146"/>
+      <c r="E24" s="146"/>
+      <c r="F24" s="146"/>
+      <c r="G24" s="146"/>
+      <c r="H24" s="146"/>
+      <c r="I24" s="146"/>
+      <c r="J24" s="146"/>
+      <c r="K24" s="146"/>
+      <c r="L24" s="146"/>
+      <c r="M24" s="146"/>
+      <c r="N24" s="146"/>
+    </row>
+    <row r="25" spans="1:16" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D25" s="146"/>
+      <c r="E25" s="146"/>
+      <c r="F25" s="146"/>
+      <c r="G25" s="146"/>
+      <c r="H25" s="146"/>
+      <c r="I25" s="146"/>
+      <c r="J25" s="146"/>
+      <c r="K25" s="146"/>
+      <c r="L25" s="146"/>
+      <c r="M25" s="146"/>
+      <c r="N25" s="146"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="J1:K2"/>
+    <mergeCell ref="B1:E2"/>
+    <mergeCell ref="F1:I2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="D20:N25"/>
     <mergeCell ref="H3:H4"/>
@@ -3511,13 +3534,6 @@
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="J1:K2"/>
-    <mergeCell ref="B1:E2"/>
-    <mergeCell ref="F1:I2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -3527,9 +3543,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3E9F1C8-DABE-4F17-BF70-F15A1A832000}">
   <dimension ref="C4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="4" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C4" s="74"/>
     </row>
   </sheetData>

--- a/2026/CABRERA/Septiembre/Septiembre CABRERA.xlsx
+++ b/2026/CABRERA/Septiembre/Septiembre CABRERA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\CABRERA\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358C7D1A-5379-43F1-A5BC-DCB748964283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{559F7CD7-2B7E-43EA-8FEF-1DD1D2B668EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="138">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -445,6 +445,9 @@
   </si>
   <si>
     <t>PREVISION ORDINARIA - AUMENTO SERVICIO DE LIMPIEZA</t>
+  </si>
+  <si>
+    <t>En S3ptiembr3 nos queda una diferencia de caja - En el banco tenemos $8.362 mas que en el excel</t>
   </si>
 </sst>
 </file>
@@ -1239,9 +1242,6 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1269,6 +1269,54 @@
     <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1278,9 +1326,6 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1290,9 +1335,6 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1308,47 +1350,8 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1777,41 +1780,41 @@
       <c r="D3" s="70"/>
     </row>
     <row r="4" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="135" t="s">
+      <c r="A4" s="134" t="s">
         <v>107</v>
       </c>
-      <c r="B4" s="135"/>
+      <c r="B4" s="134"/>
       <c r="C4" s="71"/>
       <c r="D4" s="71"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="135"/>
-      <c r="B5" s="135"/>
+      <c r="A5" s="134"/>
+      <c r="B5" s="134"/>
       <c r="C5" s="71"/>
       <c r="D5" s="71"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="135"/>
-      <c r="B6" s="135"/>
+      <c r="A6" s="134"/>
+      <c r="B6" s="134"/>
       <c r="C6" s="71"/>
       <c r="D6" s="71"/>
     </row>
     <row r="7" spans="1:8" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="135"/>
-      <c r="B7" s="135"/>
+      <c r="A7" s="134"/>
+      <c r="B7" s="134"/>
       <c r="C7" s="71"/>
       <c r="D7" s="71"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="143" t="s">
+      <c r="B9" s="142" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="143"/>
+      <c r="B10" s="142"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="143"/>
+      <c r="B11" s="142"/>
     </row>
     <row r="13" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F13" t="s">
@@ -1825,30 +1828,30 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="136" t="s">
+      <c r="A14" s="135" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="136"/>
-      <c r="C14" s="136"/>
-      <c r="D14" s="136"/>
+      <c r="B14" s="135"/>
+      <c r="C14" s="135"/>
+      <c r="D14" s="135"/>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="136"/>
-      <c r="B15" s="136"/>
-      <c r="C15" s="136"/>
-      <c r="D15" s="136"/>
+      <c r="A15" s="135"/>
+      <c r="B15" s="135"/>
+      <c r="C15" s="135"/>
+      <c r="D15" s="135"/>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="136"/>
-      <c r="B16" s="136"/>
-      <c r="C16" s="136"/>
-      <c r="D16" s="136"/>
+      <c r="A16" s="135"/>
+      <c r="B16" s="135"/>
+      <c r="C16" s="135"/>
+      <c r="D16" s="135"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="136"/>
-      <c r="B17" s="136"/>
-      <c r="C17" s="136"/>
-      <c r="D17" s="136"/>
+      <c r="A17" s="135"/>
+      <c r="B17" s="135"/>
+      <c r="C17" s="135"/>
+      <c r="D17" s="135"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="60"/>
@@ -1990,10 +1993,10 @@
       <c r="D33" s="29"/>
     </row>
     <row r="34" spans="1:6" s="15" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="141" t="s">
+      <c r="A34" s="140" t="s">
         <v>116</v>
       </c>
-      <c r="B34" s="142"/>
+      <c r="B34" s="141"/>
       <c r="C34" s="133">
         <v>87671</v>
       </c>
@@ -2148,10 +2151,10 @@
       <c r="D48" s="52"/>
     </row>
     <row r="49" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="141" t="s">
+      <c r="A49" s="140" t="s">
         <v>117</v>
       </c>
-      <c r="B49" s="142"/>
+      <c r="B49" s="141"/>
       <c r="C49" s="84">
         <v>73200</v>
       </c>
@@ -2160,10 +2163,10 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="141" t="s">
+      <c r="A50" s="140" t="s">
         <v>129</v>
       </c>
-      <c r="B50" s="142"/>
+      <c r="B50" s="141"/>
       <c r="C50" s="84">
         <v>75000</v>
       </c>
@@ -2206,8 +2209,7 @@
       </c>
       <c r="B54" s="45"/>
       <c r="C54" s="84">
-        <f>48778.75-8362</f>
-        <v>40416.75</v>
+        <v>48778.75</v>
       </c>
       <c r="D54" s="54"/>
     </row>
@@ -2219,7 +2221,7 @@
       <c r="C55" s="57"/>
       <c r="D55" s="49">
         <f>SUM(C53:C54)</f>
-        <v>109416.75</v>
+        <v>117778.75</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2229,11 +2231,11 @@
       <c r="D56" s="58"/>
     </row>
     <row r="57" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="137" t="s">
+      <c r="A57" s="136" t="s">
         <v>136</v>
       </c>
-      <c r="B57" s="138"/>
-      <c r="C57" s="139"/>
+      <c r="B57" s="137"/>
+      <c r="C57" s="138"/>
       <c r="D57" s="59">
         <v>76000</v>
       </c>
@@ -2253,7 +2255,7 @@
       <c r="C59" s="62"/>
       <c r="D59" s="63">
         <f>(SUM(D24:D57))</f>
-        <v>2266996.27</v>
+        <v>2275358.27</v>
       </c>
       <c r="E59" s="18"/>
       <c r="F59" s="18"/>
@@ -2280,14 +2282,14 @@
       <c r="D62" s="65"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="141"/>
-      <c r="B63" s="142"/>
+      <c r="A63" s="140"/>
+      <c r="B63" s="141"/>
       <c r="C63" s="53"/>
       <c r="D63" s="51"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="141"/>
-      <c r="B64" s="142"/>
+      <c r="A64" s="140"/>
+      <c r="B64" s="141"/>
       <c r="C64" s="53"/>
       <c r="D64" s="51"/>
     </row>
@@ -2351,7 +2353,7 @@
       </c>
       <c r="B73" s="125">
         <f>D59</f>
-        <v>2266996.27</v>
+        <v>2275358.27</v>
       </c>
       <c r="C73" s="126"/>
     </row>
@@ -2361,7 +2363,7 @@
       </c>
       <c r="B74" s="125">
         <f>D59-D57</f>
-        <v>2190996.27</v>
+        <v>2199358.27</v>
       </c>
       <c r="C74" s="60"/>
     </row>
@@ -2416,7 +2418,14 @@
       </c>
       <c r="C81" s="126"/>
       <c r="D81" s="18"/>
-      <c r="G81" s="134"/>
+      <c r="F81" s="170" t="s">
+        <v>137</v>
+      </c>
+      <c r="G81" s="170"/>
+      <c r="H81" s="170"/>
+      <c r="I81" s="170"/>
+      <c r="J81" s="170"/>
+      <c r="K81" s="170"/>
     </row>
     <row r="82" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="97" t="s">
@@ -2426,7 +2435,12 @@
         <f>PRORRATEO!G18</f>
         <v>2141344.5600000005</v>
       </c>
-      <c r="G82" s="134"/>
+      <c r="F82" s="170"/>
+      <c r="G82" s="170"/>
+      <c r="H82" s="170"/>
+      <c r="I82" s="170"/>
+      <c r="J82" s="170"/>
+      <c r="K82" s="170"/>
     </row>
     <row r="83" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="97" t="s">
@@ -2436,7 +2450,12 @@
         <f>B93</f>
         <v>0</v>
       </c>
-      <c r="G83" s="134"/>
+      <c r="F83" s="170"/>
+      <c r="G83" s="170"/>
+      <c r="H83" s="170"/>
+      <c r="I83" s="170"/>
+      <c r="J83" s="170"/>
+      <c r="K83" s="170"/>
     </row>
     <row r="84" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
@@ -2444,9 +2463,14 @@
       </c>
       <c r="B84" s="77">
         <f>-B74</f>
-        <v>-2190996.27</v>
-      </c>
-      <c r="G84" s="134"/>
+        <v>-2199358.27</v>
+      </c>
+      <c r="F84" s="170"/>
+      <c r="G84" s="170"/>
+      <c r="H84" s="170"/>
+      <c r="I84" s="170"/>
+      <c r="J84" s="170"/>
+      <c r="K84" s="170"/>
     </row>
     <row r="85" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
@@ -2456,7 +2480,12 @@
         <f>-(B75)</f>
         <v>0</v>
       </c>
-      <c r="G85" s="134"/>
+      <c r="F85" s="170"/>
+      <c r="G85" s="170"/>
+      <c r="H85" s="170"/>
+      <c r="I85" s="170"/>
+      <c r="J85" s="170"/>
+      <c r="K85" s="170"/>
     </row>
     <row r="86" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="98" t="s">
@@ -2464,25 +2493,30 @@
       </c>
       <c r="B86" s="68">
         <f>SUM(B81:B85)</f>
-        <v>63212.700000000652</v>
+        <v>54850.700000000652</v>
       </c>
       <c r="C86" s="18"/>
       <c r="D86" s="18"/>
-      <c r="G86" s="134"/>
+      <c r="F86" s="170"/>
+      <c r="G86" s="170"/>
+      <c r="H86" s="170"/>
+      <c r="I86" s="170"/>
+      <c r="J86" s="170"/>
+      <c r="K86" s="170"/>
     </row>
     <row r="87" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="17"/>
       <c r="C87" s="18"/>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A89" s="140" t="s">
+      <c r="A89" s="139" t="s">
         <v>38</v>
       </c>
-      <c r="B89" s="140"/>
+      <c r="B89" s="139"/>
     </row>
     <row r="90" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="140"/>
-      <c r="B90" s="140"/>
+      <c r="A90" s="139"/>
+      <c r="B90" s="139"/>
     </row>
     <row r="91" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="66"/>
@@ -2506,7 +2540,6 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="G81:G86"/>
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A14:D17"/>
     <mergeCell ref="A57:C57"/>
@@ -2517,6 +2550,7 @@
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="A49:B49"/>
     <mergeCell ref="A50:B50"/>
+    <mergeCell ref="F81:K86"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2551,26 +2585,26 @@
   <sheetData>
     <row r="1" spans="1:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
-      <c r="B1" s="161" t="str">
+      <c r="B1" s="147" t="str">
         <f>RESUMEN!A4</f>
         <v>Banco: Santander
 C.U.I.T.   30-71774143-5
 CBU: 0720533020000000956840 ALIAS: BLONDA.LAGO.CORO
 Nº de cuenta: 533-009568/4</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
-      <c r="F1" s="161" t="s">
+      <c r="C1" s="148"/>
+      <c r="D1" s="148"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="147" t="s">
         <v>111</v>
       </c>
-      <c r="G1" s="162"/>
-      <c r="H1" s="162"/>
-      <c r="I1" s="163"/>
-      <c r="J1" s="157" t="s">
+      <c r="G1" s="148"/>
+      <c r="H1" s="148"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="143" t="s">
         <v>108</v>
       </c>
-      <c r="K1" s="158"/>
+      <c r="K1" s="144"/>
       <c r="L1" s="103" t="s">
         <v>109</v>
       </c>
@@ -2583,16 +2617,16 @@
     </row>
     <row r="2" spans="1:18" ht="43.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
-      <c r="B2" s="164"/>
-      <c r="C2" s="165"/>
-      <c r="D2" s="165"/>
-      <c r="E2" s="166"/>
-      <c r="F2" s="164"/>
-      <c r="G2" s="165"/>
-      <c r="H2" s="165"/>
-      <c r="I2" s="166"/>
-      <c r="J2" s="159"/>
-      <c r="K2" s="160"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="151"/>
+      <c r="D2" s="151"/>
+      <c r="E2" s="152"/>
+      <c r="F2" s="150"/>
+      <c r="G2" s="151"/>
+      <c r="H2" s="151"/>
+      <c r="I2" s="152"/>
+      <c r="J2" s="145"/>
+      <c r="K2" s="146"/>
       <c r="L2" s="104" t="s">
         <v>110</v>
       </c>
@@ -2601,72 +2635,72 @@
       <c r="O2" s="100"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="167" t="s">
+      <c r="A3" s="153" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="155" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="147" t="s">
+      <c r="C3" s="157" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="147" t="s">
+      <c r="D3" s="157" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="147" t="s">
+      <c r="E3" s="157" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="147" t="s">
+      <c r="F3" s="157" t="s">
         <v>46</v>
       </c>
-      <c r="G3" s="147" t="s">
+      <c r="G3" s="157" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="147" t="s">
+      <c r="H3" s="157" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="152" t="s">
+      <c r="I3" s="165" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="149" t="s">
+      <c r="J3" s="163" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="149" t="s">
+      <c r="K3" s="163" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="149" t="s">
+      <c r="L3" s="163" t="s">
         <v>33</v>
       </c>
-      <c r="M3" s="155" t="s">
+      <c r="M3" s="168" t="s">
         <v>44</v>
       </c>
       <c r="N3" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="O3" s="144" t="s">
+      <c r="O3" s="159" t="s">
         <v>42</v>
       </c>
       <c r="R3" s="18"/>
     </row>
     <row r="4" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="168"/>
-      <c r="B4" s="170"/>
-      <c r="C4" s="151"/>
-      <c r="D4" s="151"/>
-      <c r="E4" s="148"/>
-      <c r="F4" s="151"/>
-      <c r="G4" s="151"/>
-      <c r="H4" s="148"/>
-      <c r="I4" s="153"/>
-      <c r="J4" s="150"/>
-      <c r="K4" s="154"/>
-      <c r="L4" s="150"/>
-      <c r="M4" s="156"/>
+      <c r="A4" s="154"/>
+      <c r="B4" s="156"/>
+      <c r="C4" s="158"/>
+      <c r="D4" s="158"/>
+      <c r="E4" s="162"/>
+      <c r="F4" s="158"/>
+      <c r="G4" s="158"/>
+      <c r="H4" s="162"/>
+      <c r="I4" s="166"/>
+      <c r="J4" s="164"/>
+      <c r="K4" s="167"/>
+      <c r="L4" s="164"/>
+      <c r="M4" s="169"/>
       <c r="N4" s="24" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 16/10</v>
       </c>
-      <c r="O4" s="145"/>
+      <c r="O4" s="160"/>
     </row>
     <row r="5" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -3435,94 +3469,87 @@
       <c r="D19" s="20"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D20" s="146" t="s">
+      <c r="D20" s="161" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="146"/>
-      <c r="F20" s="146"/>
-      <c r="G20" s="146"/>
-      <c r="H20" s="146"/>
-      <c r="I20" s="146"/>
-      <c r="J20" s="146"/>
-      <c r="K20" s="146"/>
-      <c r="L20" s="146"/>
-      <c r="M20" s="146"/>
-      <c r="N20" s="146"/>
+      <c r="E20" s="161"/>
+      <c r="F20" s="161"/>
+      <c r="G20" s="161"/>
+      <c r="H20" s="161"/>
+      <c r="I20" s="161"/>
+      <c r="J20" s="161"/>
+      <c r="K20" s="161"/>
+      <c r="L20" s="161"/>
+      <c r="M20" s="161"/>
+      <c r="N20" s="161"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D21" s="146"/>
-      <c r="E21" s="146"/>
-      <c r="F21" s="146"/>
-      <c r="G21" s="146"/>
-      <c r="H21" s="146"/>
-      <c r="I21" s="146"/>
-      <c r="J21" s="146"/>
-      <c r="K21" s="146"/>
-      <c r="L21" s="146"/>
-      <c r="M21" s="146"/>
-      <c r="N21" s="146"/>
+      <c r="D21" s="161"/>
+      <c r="E21" s="161"/>
+      <c r="F21" s="161"/>
+      <c r="G21" s="161"/>
+      <c r="H21" s="161"/>
+      <c r="I21" s="161"/>
+      <c r="J21" s="161"/>
+      <c r="K21" s="161"/>
+      <c r="L21" s="161"/>
+      <c r="M21" s="161"/>
+      <c r="N21" s="161"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D22" s="146"/>
-      <c r="E22" s="146"/>
-      <c r="F22" s="146"/>
-      <c r="G22" s="146"/>
-      <c r="H22" s="146"/>
-      <c r="I22" s="146"/>
-      <c r="J22" s="146"/>
-      <c r="K22" s="146"/>
-      <c r="L22" s="146"/>
-      <c r="M22" s="146"/>
-      <c r="N22" s="146"/>
+      <c r="D22" s="161"/>
+      <c r="E22" s="161"/>
+      <c r="F22" s="161"/>
+      <c r="G22" s="161"/>
+      <c r="H22" s="161"/>
+      <c r="I22" s="161"/>
+      <c r="J22" s="161"/>
+      <c r="K22" s="161"/>
+      <c r="L22" s="161"/>
+      <c r="M22" s="161"/>
+      <c r="N22" s="161"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D23" s="146"/>
-      <c r="E23" s="146"/>
-      <c r="F23" s="146"/>
-      <c r="G23" s="146"/>
-      <c r="H23" s="146"/>
-      <c r="I23" s="146"/>
-      <c r="J23" s="146"/>
-      <c r="K23" s="146"/>
-      <c r="L23" s="146"/>
-      <c r="M23" s="146"/>
-      <c r="N23" s="146"/>
+      <c r="D23" s="161"/>
+      <c r="E23" s="161"/>
+      <c r="F23" s="161"/>
+      <c r="G23" s="161"/>
+      <c r="H23" s="161"/>
+      <c r="I23" s="161"/>
+      <c r="J23" s="161"/>
+      <c r="K23" s="161"/>
+      <c r="L23" s="161"/>
+      <c r="M23" s="161"/>
+      <c r="N23" s="161"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D24" s="146"/>
-      <c r="E24" s="146"/>
-      <c r="F24" s="146"/>
-      <c r="G24" s="146"/>
-      <c r="H24" s="146"/>
-      <c r="I24" s="146"/>
-      <c r="J24" s="146"/>
-      <c r="K24" s="146"/>
-      <c r="L24" s="146"/>
-      <c r="M24" s="146"/>
-      <c r="N24" s="146"/>
+      <c r="D24" s="161"/>
+      <c r="E24" s="161"/>
+      <c r="F24" s="161"/>
+      <c r="G24" s="161"/>
+      <c r="H24" s="161"/>
+      <c r="I24" s="161"/>
+      <c r="J24" s="161"/>
+      <c r="K24" s="161"/>
+      <c r="L24" s="161"/>
+      <c r="M24" s="161"/>
+      <c r="N24" s="161"/>
     </row>
     <row r="25" spans="1:16" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D25" s="146"/>
-      <c r="E25" s="146"/>
-      <c r="F25" s="146"/>
-      <c r="G25" s="146"/>
-      <c r="H25" s="146"/>
-      <c r="I25" s="146"/>
-      <c r="J25" s="146"/>
-      <c r="K25" s="146"/>
-      <c r="L25" s="146"/>
-      <c r="M25" s="146"/>
-      <c r="N25" s="146"/>
+      <c r="D25" s="161"/>
+      <c r="E25" s="161"/>
+      <c r="F25" s="161"/>
+      <c r="G25" s="161"/>
+      <c r="H25" s="161"/>
+      <c r="I25" s="161"/>
+      <c r="J25" s="161"/>
+      <c r="K25" s="161"/>
+      <c r="L25" s="161"/>
+      <c r="M25" s="161"/>
+      <c r="N25" s="161"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="J1:K2"/>
-    <mergeCell ref="B1:E2"/>
-    <mergeCell ref="F1:I2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="D20:N25"/>
     <mergeCell ref="H3:H4"/>
@@ -3534,6 +3561,13 @@
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="E3:E4"/>
+    <mergeCell ref="J1:K2"/>
+    <mergeCell ref="B1:E2"/>
+    <mergeCell ref="F1:I2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
